--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5179A66-50A2-4D18-9A76-167F4287150D}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AF1E7DD-C5B2-4AED-ABDC-DD2F4F42F540}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8858" uniqueCount="5912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8861" uniqueCount="5914">
   <si>
     <t>Unidade</t>
   </si>
@@ -17775,6 +17775,12 @@
   </si>
   <si>
     <t>SUPORTE PARA TV BI-ARTICULADO - PARA TV'S DE 10 A 60 POLEGADAS - COR PRETO</t>
+  </si>
+  <si>
+    <t>U.02.2007</t>
+  </si>
+  <si>
+    <t>BASE MISTURADOR MONOCOMANDO  KOHLER</t>
   </si>
 </sst>
 </file>
@@ -17842,15 +17848,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{632AACD3-B970-4B85-9519-77FD5FF68333}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18195,7 +18193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2952"/>
+  <dimension ref="A1:E2953"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51435,9 +51433,20 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2953" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2953" t="s">
+        <v>5912</v>
+      </c>
+      <c r="B2953" t="s">
+        <v>5913</v>
+      </c>
+      <c r="C2953" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DF1FEEB-D05A-446E-A3FD-23F5FFB4ABE1}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78D269D9-AFF6-46DB-A5CB-4F29A795C122}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8816" uniqueCount="5886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8819" uniqueCount="5888">
   <si>
     <t>Unidade</t>
   </si>
@@ -17697,6 +17697,12 @@
   </si>
   <si>
     <t>VB</t>
+  </si>
+  <si>
+    <t>S.11.0001</t>
+  </si>
+  <si>
+    <t>GALVANIZAÇÃO</t>
   </si>
 </sst>
 </file>
@@ -18109,7 +18115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2938"/>
+  <dimension ref="A1:E2939"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51195,6 +51201,17 @@
         <v>5885</v>
       </c>
     </row>
+    <row r="2939" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2939" t="s">
+        <v>5886</v>
+      </c>
+      <c r="B2939" t="s">
+        <v>5887</v>
+      </c>
+      <c r="C2939" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78D269D9-AFF6-46DB-A5CB-4F29A795C122}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FC3F102-B418-4CBF-A989-4112CA36D8E2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8819" uniqueCount="5888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8831" uniqueCount="5896">
   <si>
     <t>Unidade</t>
   </si>
@@ -17703,6 +17703,30 @@
   </si>
   <si>
     <t>GALVANIZAÇÃO</t>
+  </si>
+  <si>
+    <t>W.09.0005</t>
+  </si>
+  <si>
+    <t>W.09.0007</t>
+  </si>
+  <si>
+    <t>MARCADOR INDUSTRIAL TIPO CANETA</t>
+  </si>
+  <si>
+    <t>MARCADOR INDUSTRIAL TIPO BISNAGA</t>
+  </si>
+  <si>
+    <t>W.09.0004</t>
+  </si>
+  <si>
+    <t>MASSA DE VIDRO PARA VIDRACEIRO</t>
+  </si>
+  <si>
+    <t>W.09.0006</t>
+  </si>
+  <si>
+    <t>MANGUEIRA DE PVC CRISTAL TRANÇADA PT 250 - 1/4 POL</t>
   </si>
 </sst>
 </file>
@@ -18115,7 +18139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2939"/>
+  <dimension ref="A1:E2943"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51212,6 +51236,50 @@
         <v>13</v>
       </c>
     </row>
+    <row r="2940" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2940" t="s">
+        <v>5888</v>
+      </c>
+      <c r="B2940" t="s">
+        <v>5890</v>
+      </c>
+      <c r="C2940" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2941" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2941" t="s">
+        <v>5889</v>
+      </c>
+      <c r="B2941" t="s">
+        <v>5891</v>
+      </c>
+      <c r="C2941" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2942" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2942" t="s">
+        <v>5892</v>
+      </c>
+      <c r="B2942" t="s">
+        <v>5893</v>
+      </c>
+      <c r="C2942" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2943" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2943" t="s">
+        <v>5894</v>
+      </c>
+      <c r="B2943" t="s">
+        <v>5895</v>
+      </c>
+      <c r="C2943" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FC3F102-B418-4CBF-A989-4112CA36D8E2}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D7E2D05-E454-464F-9BDB-DAE6BF2939D2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8831" uniqueCount="5896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8834" uniqueCount="5898">
   <si>
     <t>Unidade</t>
   </si>
@@ -17727,6 +17727,12 @@
   </si>
   <si>
     <t>MANGUEIRA DE PVC CRISTAL TRANÇADA PT 250 - 1/4 POL</t>
+  </si>
+  <si>
+    <t>H.06.1928</t>
+  </si>
+  <si>
+    <t>TUBO QUADRADO GALVANIZADO ( METALON ) 20 X 20 X 0,95MM</t>
   </si>
 </sst>
 </file>
@@ -18139,7 +18145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2943"/>
+  <dimension ref="A1:E2944"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51280,6 +51286,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2944" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2944" t="s">
+        <v>5896</v>
+      </c>
+      <c r="B2944" t="s">
+        <v>5897</v>
+      </c>
+      <c r="C2944" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D7E2D05-E454-464F-9BDB-DAE6BF2939D2}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD3714D3-6C0E-4F04-9DB6-63343BCEA231}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8834" uniqueCount="5898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8837" uniqueCount="5900">
   <si>
     <t>Unidade</t>
   </si>
@@ -17733,6 +17733,12 @@
   </si>
   <si>
     <t>TUBO QUADRADO GALVANIZADO ( METALON ) 20 X 20 X 0,95MM</t>
+  </si>
+  <si>
+    <t>H.11.0681</t>
+  </si>
+  <si>
+    <t>TUBO DE AÇO GALVANIZADO PRA LINHA DE VIDA 3" COM 3MM ESPESSURA</t>
   </si>
 </sst>
 </file>
@@ -18145,7 +18151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2944"/>
+  <dimension ref="A1:E2945"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51297,6 +51303,17 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2945" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2945" t="s">
+        <v>5898</v>
+      </c>
+      <c r="B2945" t="s">
+        <v>5899</v>
+      </c>
+      <c r="C2945" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD3714D3-6C0E-4F04-9DB6-63343BCEA231}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A89B311-C934-42B2-8388-73177CD7C983}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
+    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8837" uniqueCount="5900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8840" uniqueCount="5902">
   <si>
     <t>Unidade</t>
   </si>
@@ -17739,6 +17739,12 @@
   </si>
   <si>
     <t>TUBO DE AÇO GALVANIZADO PRA LINHA DE VIDA 3" COM 3MM ESPESSURA</t>
+  </si>
+  <si>
+    <t>S.08.0001</t>
+  </si>
+  <si>
+    <t>MANTA ASFÁLTICA - 3 MM</t>
   </si>
 </sst>
 </file>
@@ -18151,7 +18157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2945"/>
+  <dimension ref="A1:E2946"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51314,6 +51320,17 @@
         <v>23</v>
       </c>
     </row>
+    <row r="2946" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2946" t="s">
+        <v>5900</v>
+      </c>
+      <c r="B2946" t="s">
+        <v>5901</v>
+      </c>
+      <c r="C2946" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A89B311-C934-42B2-8388-73177CD7C983}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{398362D2-10E1-447A-BAB5-A4E09E5C034B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$2951</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$2946</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8840" uniqueCount="5902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8843" uniqueCount="5904">
   <si>
     <t>Unidade</t>
   </si>
@@ -17745,6 +17745,12 @@
   </si>
   <si>
     <t>MANTA ASFÁLTICA - 3 MM</t>
+  </si>
+  <si>
+    <t>G.03.0002</t>
+  </si>
+  <si>
+    <t>CAÇAMBA - UNIDADE</t>
   </si>
 </sst>
 </file>
@@ -18157,7 +18163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2946"/>
+  <dimension ref="A1:E2947"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51331,6 +51337,17 @@
         <v>26</v>
       </c>
     </row>
+    <row r="2947" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2947" t="s">
+        <v>5902</v>
+      </c>
+      <c r="B2947" t="s">
+        <v>5903</v>
+      </c>
+      <c r="C2947" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{398362D2-10E1-447A-BAB5-A4E09E5C034B}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C14570E-C2BA-4C74-A9E8-E1BF5001A63A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8843" uniqueCount="5904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8846" uniqueCount="5906">
   <si>
     <t>Unidade</t>
   </si>
@@ -17751,6 +17751,12 @@
   </si>
   <si>
     <t>CAÇAMBA - UNIDADE</t>
+  </si>
+  <si>
+    <t>E.05.0010</t>
+  </si>
+  <si>
+    <t>PRANCHA DE RESGATE COMPENSADO NAVAL COM CINTO</t>
   </si>
 </sst>
 </file>
@@ -18163,7 +18169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2947"/>
+  <dimension ref="A1:E2948"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51348,6 +51354,17 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2948" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2948" t="s">
+        <v>5904</v>
+      </c>
+      <c r="B2948" t="s">
+        <v>5905</v>
+      </c>
+      <c r="C2948" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C14570E-C2BA-4C74-A9E8-E1BF5001A63A}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{797A07B8-CF2C-4D4C-ACE7-79074D5FE2E4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$2946</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$2949</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8846" uniqueCount="5906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8849" uniqueCount="5908">
   <si>
     <t>Unidade</t>
   </si>
@@ -17757,6 +17757,12 @@
   </si>
   <si>
     <t>PRANCHA DE RESGATE COMPENSADO NAVAL COM CINTO</t>
+  </si>
+  <si>
+    <t>N.01.0001</t>
+  </si>
+  <si>
+    <t>TECNOCIMENTO</t>
   </si>
 </sst>
 </file>
@@ -18169,7 +18175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2948"/>
+  <dimension ref="A1:E2949"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51365,7 +51371,19 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2949" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2949" t="s">
+        <v>5906</v>
+      </c>
+      <c r="B2949" t="s">
+        <v>5907</v>
+      </c>
+      <c r="C2949" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E2949" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}"/>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{797A07B8-CF2C-4D4C-ACE7-79074D5FE2E4}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC5E9E7A-D94F-4116-B69C-9CD24F0B6EC6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
+    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8849" uniqueCount="5908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8852" uniqueCount="5909">
   <si>
     <t>Unidade</t>
   </si>
@@ -17763,6 +17763,9 @@
   </si>
   <si>
     <t>TECNOCIMENTO</t>
+  </si>
+  <si>
+    <t>BLOCO CERÂMICO 09 X 19 X 29</t>
   </si>
 </sst>
 </file>
@@ -17852,10 +17855,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18175,7 +18174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E2949"/>
+  <dimension ref="A1:E2950"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -51382,6 +51381,17 @@
         <v>82</v>
       </c>
     </row>
+    <row r="2950" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2950" t="s">
+        <v>4016</v>
+      </c>
+      <c r="B2950" t="s">
+        <v>5908</v>
+      </c>
+      <c r="C2950" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E2949" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}"/>
   <conditionalFormatting sqref="A129:A794 A1:A126 A3716:A1048576 A920:A2932">

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C76588A2-BF5D-48C1-84FC-9135AEEE7C96}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF453E7E-9EF0-4363-A34C-1FAE271DF340}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4950" windowWidth="29040" windowHeight="15720" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9071" uniqueCount="6057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9074" uniqueCount="6059">
   <si>
     <t>Unidade</t>
   </si>
@@ -18210,6 +18210,12 @@
   </si>
   <si>
     <t>CAIXA ORGANIZADORA - 5 LITROS - COR PRETA</t>
+  </si>
+  <si>
+    <t>K.04.0001</t>
+  </si>
+  <si>
+    <t>DETECTOR DE FUMAÇA</t>
   </si>
 </sst>
 </file>
@@ -18279,61 +18285,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{632AACD3-B970-4B85-9519-77FD5FF68333}"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18678,7 +18630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E3023"/>
+  <dimension ref="A1:E3024"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -52699,9 +52651,20 @@
         <v>4</v>
       </c>
     </row>
+    <row r="3024" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3024" t="s">
+        <v>6057</v>
+      </c>
+      <c r="B3024" t="s">
+        <v>6058</v>
+      </c>
+      <c r="C3024" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Insumos.xlsx
+++ b/Insumos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/Formulario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9FECF73-011C-46AC-9666-313F9F085EC3}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{B1C9BEE0-D8AB-41A6-9B3F-41E286CEEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5DEB454-C9E8-4013-8CB0-31ED3FD85FBF}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3720" windowWidth="29040" windowHeight="15720" xr2:uid="{D0464B66-1327-441A-BC0B-79C1075B3A87}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5753" uniqueCount="3852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5756" uniqueCount="3854">
   <si>
     <t>Unidade</t>
   </si>
@@ -11595,6 +11595,12 @@
   </si>
   <si>
     <t>MISTURADOR MONOCOMANDO DE PISO PARA BANHEIRA REDONDO INOX - DECA - 1871.INX104</t>
+  </si>
+  <si>
+    <t>K.02.0701</t>
+  </si>
+  <si>
+    <t>MATERIAL - ED</t>
   </si>
 </sst>
 </file>
@@ -12010,7 +12016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32D2B19-46D2-47DB-8479-E6FC0B3CCBCE}">
-  <dimension ref="A1:E1917"/>
+  <dimension ref="A1:E1918"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -33913,6 +33919,17 @@
         <v>4</v>
       </c>
     </row>
+    <row r="1918" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1918" t="s">
+        <v>3852</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>3853</v>
+      </c>
+      <c r="C1918" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A3024:A1048576 A1:A1918 A2829">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
